--- a/游戏设计王/老虎机数学专题-消除掉落.xlsx
+++ b/游戏设计王/老虎机数学专题-消除掉落.xlsx
@@ -220,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -228,6 +228,7 @@
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="0.0000%"/>
     <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -920,7 +921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1010,6 +1011,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3269,15 +3276,15 @@
       <c r="A8" s="3">
         <v>1</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="47">
         <f t="shared" ref="B8:B19" si="0">$B$4*$B$5^(A8-1)*(1-$B$5)</f>
         <v>0.15</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="47">
         <f t="shared" ref="C8:C19" si="1">$B$4*$B$5^(A8-1)</f>
         <v>0.25</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="47">
         <f>SUM($B$8:$B8)</f>
         <v>0.15</v>
       </c>
@@ -3286,15 +3293,15 @@
       <c r="A9" s="3">
         <v>2</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="47">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="47">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="47">
         <f>SUM($B$8:$B9)</f>
         <v>0.21</v>
       </c>
@@ -3303,15 +3310,15 @@
       <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="47">
         <f t="shared" si="0"/>
         <v>0.024</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="47">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="47">
         <f>SUM($B$8:$B10)</f>
         <v>0.234</v>
       </c>
@@ -3320,15 +3327,15 @@
       <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="47">
         <f t="shared" si="0"/>
         <v>0.0096</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="47">
         <f t="shared" si="1"/>
         <v>0.016</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="47">
         <f>SUM($B$8:$B11)</f>
         <v>0.2436</v>
       </c>
@@ -3337,15 +3344,15 @@
       <c r="A12" s="3">
         <v>5</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="47">
         <f t="shared" si="0"/>
         <v>0.00384</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="47">
         <f t="shared" si="1"/>
         <v>0.0064</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="47">
         <f>SUM($B$8:$B12)</f>
         <v>0.24744</v>
       </c>
@@ -3354,15 +3361,15 @@
       <c r="A13" s="3">
         <v>6</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>0.001536</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="47">
         <f t="shared" si="1"/>
         <v>0.00256</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="47">
         <f>SUM($B$8:$B13)</f>
         <v>0.248976</v>
       </c>
@@ -3371,15 +3378,15 @@
       <c r="A14" s="3">
         <v>7</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="47">
         <f t="shared" si="0"/>
         <v>0.0006144</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="47">
         <f t="shared" si="1"/>
         <v>0.001024</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="47">
         <f>SUM($B$8:$B14)</f>
         <v>0.2495904</v>
       </c>
@@ -3388,15 +3395,15 @@
       <c r="A15" s="3">
         <v>8</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>0.00024576</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="47">
         <f t="shared" si="1"/>
         <v>0.0004096</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="47">
         <f>SUM($B$8:$B15)</f>
         <v>0.24983616</v>
       </c>
@@ -3405,15 +3412,15 @@
       <c r="A16" s="3">
         <v>9</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="47">
         <f t="shared" si="0"/>
         <v>9.83040000000001e-5</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="47">
         <f t="shared" si="1"/>
         <v>0.00016384</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="47">
         <f>SUM($B$8:$B16)</f>
         <v>0.249934464</v>
       </c>
@@ -3422,15 +3429,15 @@
       <c r="A17" s="3">
         <v>10</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>3.93216e-5</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="47">
         <f t="shared" si="1"/>
         <v>6.5536e-5</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="47">
         <f>SUM($B$8:$B17)</f>
         <v>0.2499737856</v>
       </c>
@@ -3439,15 +3446,15 @@
       <c r="A18" s="3">
         <v>11</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="47">
         <f t="shared" si="0"/>
         <v>1.572864e-5</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="47">
         <f t="shared" si="1"/>
         <v>2.62144e-5</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="47">
         <f>SUM($B$8:$B18)</f>
         <v>0.24998951424</v>
       </c>
@@ -3456,15 +3463,15 @@
       <c r="A19" s="3">
         <v>12</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>6.291456e-6</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="47">
         <f t="shared" si="1"/>
         <v>1.048576e-5</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="47">
         <f>SUM($B$8:$B19)</f>
         <v>0.249995805696</v>
       </c>
@@ -3502,7 +3509,7 @@
       <c r="A22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="47">
         <f>B4*B5^3</f>
         <v>0.016</v>
       </c>
@@ -3602,7 +3609,7 @@
       <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="48">
         <f>B27*B28</f>
         <v>1</v>
       </c>
